--- a/www/download/COUNTRY.CYP.zdW13.xlsx
+++ b/www/download/COUNTRY.CYP.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Chipre</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.772678123777948</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.796685775755041</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.877292976582033</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.883384436593682</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.926586570603177</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.06079414511591</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.09817702407959</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03987932720202</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.882706029234349</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.799673759926997</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.792091754634952</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.783471856320399</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.727151112510703</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902076410497</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948682306625</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.493623441827055</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.460065500906883</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.669270840809346</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.563856066707982</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.440062605036318</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.45636742650405</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.36783292999725</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.350212378415792</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.223111535603099</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.209344031557566</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.224013646635447</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.24456459472611</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.40083797277373</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.200110709486781</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.42549355718445</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>1.41854890287996</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1.34951879631473</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1.68889000016391</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1.56899965407052</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>1.39002305294459</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1.44463282455553</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>1.19598459907497</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>1.16748132523514</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>0.978357426070121</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1.02046847916777</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>1.0385207694644</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>1.12582089100362</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>1.38589778318367</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>1.04595472254225</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1.44353393571881</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>556.844</t>
+          <t>2.09378418895836</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>559.558</t>
+          <t>1.99598166086192</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>565.864</t>
+          <t>2.44485874467366</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>576.508</t>
+          <t>2.28600889654364</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>590.902</t>
+          <t>2.02149386643513</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>605.96</t>
+          <t>2.14633195913345</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>626.986</t>
+          <t>1.8872639560994</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>631.03</t>
+          <t>1.84214199255766</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>652.422</t>
+          <t>1.2847196678115</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>663.882</t>
+          <t>1.73790134496877</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>679.879</t>
+          <t>1.81377968031867</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>694.745</t>
+          <t>1.86747040559826</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>715.064</t>
+          <t>2.23200418259858</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>724.744</t>
+          <t>1.67070872589573</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>725.571</t>
+          <t>2.22836246111426</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>385.082</t>
+          <t>521769635.911713</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>388.735</t>
+          <t>575275302.286532</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>393.173</t>
+          <t>511188095.686683</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>400.651</t>
+          <t>516893321.414564</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>410.296</t>
+          <t>554528136.075119</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>421.155</t>
+          <t>551250148.01107</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>433.872</t>
+          <t>613085461.082389</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>443.031</t>
+          <t>634759095.068938</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>455.955</t>
+          <t>655663296.297158</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>458.638</t>
+          <t>623547900.758255</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>473.113</t>
+          <t>575805981.170818</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>494.479</t>
+          <t>592642681.030207</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>516.413</t>
+          <t>572892568.420622</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>540.57</t>
+          <t>806853858.592282</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>541.705</t>
+          <t>568208259.113876</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>180909645.797909</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>188670562.074021</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>164833654.668099</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>174803147.167746</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>194804107.043897</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>196431060.815916</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>221240642.870125</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>230497217.972361</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>267620432.865848</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>259625447.166941</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>263011882.658186</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>271126922.779541</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>255785164.290961</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>317551095.543769</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>266014707.820441</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>1716454.27564987</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>1774797.12371234</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>1748376.28752403</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>1725988.22360881</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>1912500.99375705</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>1967066.34921224</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>2014688.33859553</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>1855717.09090577</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>1604567.46310259</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>1403570.74425474</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>1172536.71881773</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>1091930.33655859</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>900411.364938282</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>1060895.51128975</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>801046.308319572</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>2269.93322256982</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>2255.05747598861</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>2233.12484983342</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>2207.44588619155</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>2300.92269805809</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>2344.29418278861</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>2290.0975590877</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>2339.14439238457</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>2594.37691705569</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>2901.23514942588</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>3123.40453925988</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>3298.89918350412</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>3782.68653840042</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>4071.02308653699</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>3841.83874355888</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>4495.81167509041</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>4992.3214954997</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>4421.93124023906</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>4426.17806849223</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>4939.16906046708</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>4991.1651471663</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>5391.05775674997</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>5703.48201998843</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>6315.69503136983</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>6606.45610093257</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>6534.13534702762</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>7020.85158173797</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>7647.04452397014</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>11791.1549239647</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>7740.6773805208</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>1.12858650234561</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>1.06039147766413</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>1.38527177064386</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>1.29201075485338</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>1.10619610525558</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>1.14403464630617</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>0.961086328313987</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>0.922066582396341</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.70373762241301</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>0.766537159607055</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>0.798827472045682</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.823791584143308</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>1.01893257348018</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.58</t>
+          <t>0.702308723181498</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>1.03637236616875</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.772678123777948</t>
+          <t>808.655819543927</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.796685775755041</t>
+          <t>835.057725985601</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.877292976582033</t>
+          <t>720.542965726301</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.883384436593682</t>
+          <t>749.306667579798</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.926586570603177</t>
+          <t>818.562940337532</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06079414511591</t>
+          <t>812.706085295475</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.09817702407959</t>
+          <t>891.380511160859</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.03987932720202</t>
+          <t>901.788802708767</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.882706029234349</t>
+          <t>1017.95524102643</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.799673759926997</t>
+          <t>947.884071438267</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.792091754634952</t>
+          <t>920.265509650755</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.783471856320399</t>
+          <t>915.659989123747</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.727151112510703</t>
+          <t>828.319832548447</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902076410497</t>
+          <t>972.293617709031</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948682306625</t>
+          <t>817.500638661467</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>17447209.0212011</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>30313596.4542484</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>969624.210725032</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>20272879.6075946</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>86379538.1930064</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>81564705.6919632</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>125800938.536359</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>80570158.3722893</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>98093841.5714373</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>87555025.7250857</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>75764983.363484</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>77503172.3894753</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>16494827.2747775</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>175535169.136543</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>76423866.277587</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>19061693.8009172</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>39135844.0185418</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>12263829.8114202</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>24581970.3738738</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>87068462.2651099</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>90561365.7525786</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>129549883.512686</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>78593504.2934864</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>108082911.627987</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>62858548.1192753</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12346358.9591649</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>38181421.8034927</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-10151204.9224878</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>141879097.856071</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>29119995.2532832</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-1614484.77971613</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-8822247.56429339</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-11294205.6006952</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-4309090.76627913</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-688924.072103485</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-8996660.06061541</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-3748944.97632689</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1976654.07880284</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-9989070.05655007</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>24696477.6058104</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>63418624.4043191</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>39321750.5859827</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>26646032.1972653</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>33656071.2804719</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47303871.0243038</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1721.29386252443</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1720.54582197833</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1718.69079568295</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1717.41894077624</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1724.05407684547</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1742.47000413736</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1748.07413376309</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1733.29812206573</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1734.32864206923</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1674.47243519533</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1655.3988803359</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1669.97298210064</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1672.32189119171</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1655.14390691978</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1664.73570989551</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1880.59439378588</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1879.60362781323</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1889.36227045075</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1895.78428148635</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1907.36604260813</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1924.90470139771</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1947.76638707673</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1922.11392019494</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1914.3838028169</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1879.08859326352</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1855.56495633188</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1865.5880773362</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1859.72431729519</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1852.77628972653</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1848.05901025774</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>49.36</t>
+          <t>1986.75605591144</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.01</t>
+          <t>2113.1513598131</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>66.93</t>
+          <t>2064.14002772178</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>56.39</t>
+          <t>2082.82920060218</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>2162.24533912994</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>2147.15485544231</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>2290.77504501028</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>2299.08485759001</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>2752.51981074515</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>3347.5841392997</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>3450.0903690429</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>3796.76966358804</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>4611.57890213568</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5147.43092485272</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>4628.49509079995</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>141.85</t>
+          <t>130036354.045944</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>134.95</t>
+          <t>144764292.299224</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>168.89</t>
+          <t>126748824.347025</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>156.9</t>
+          <t>125687367.963659</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>134499543.071491</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>144.46</t>
+          <t>140087272.065762</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>119.6</t>
+          <t>158847405.447529</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>116.75</t>
+          <t>154669939.093104</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>97.84</t>
+          <t>160180811.193136</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>102.05</t>
+          <t>135626790.552691</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>103.85</t>
+          <t>96308749.2154651</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>112.58</t>
+          <t>116044924.124023</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>138.59</t>
+          <t>127963034.067037</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>153006789.849783</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>144.35</t>
+          <t>101597708.47786</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>209.38</t>
+          <t>3903.81993369891</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>199.6</t>
+          <t>4188.43247851129</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>244.49</t>
+          <t>4019.55139186513</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>228.6</t>
+          <t>4033.88415550994</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>202.15</t>
+          <t>4092.21245558792</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>214.63</t>
+          <t>4242.13096642063</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>188.73</t>
+          <t>4402.20095822659</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>184.21</t>
+          <t>4735.10396469906</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>128.47</t>
+          <t>5495.71255800651</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>173.79</t>
+          <t>6384.3116209553</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>181.38</t>
+          <t>6664.35606501167</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>186.75</t>
+          <t>7593.47009763796</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>223.2</t>
+          <t>9632.78411611902</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>167.07</t>
+          <t>11415.8392821631</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>222.84</t>
+          <t>8671.10649166191</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>556.844</t>
+          <t>411691822.819073</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>559.558</t>
+          <t>449406046.080437</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>565.864</t>
+          <t>364338581.698052</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>576.508</t>
+          <t>396386652.19124</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>590.902</t>
+          <t>474425476.687059</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>605.96</t>
+          <t>500323206.242971</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>626.986</t>
+          <t>580563380.399245</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>631.03</t>
+          <t>572859203.745036</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>652.422</t>
+          <t>619482066.274925</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>663.882</t>
+          <t>590918927.704891</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>679.879</t>
+          <t>532559896.820413</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>694.745</t>
+          <t>583004580.11125</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>715.064</t>
+          <t>600317591.665815</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>724.744</t>
+          <t>840879139.247893</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>725.571</t>
+          <t>541904032.893372</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>385.082</t>
+          <t>-1917.06387778747</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>388.735</t>
+          <t>-2075.28111869819</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>393.173</t>
+          <t>-1955.41136414335</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>400.651</t>
+          <t>-1951.05495490776</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>410.296</t>
+          <t>-1929.96711645797</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>421.155</t>
+          <t>-2094.97611097832</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>433.872</t>
+          <t>-2111.42591321631</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>443.031</t>
+          <t>-2436.01910710905</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>455.955</t>
+          <t>-2743.19274726135</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>458.638</t>
+          <t>-3036.7274816556</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>473.113</t>
+          <t>-3214.26569596877</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>494.479</t>
+          <t>-3796.70043404992</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>516.413</t>
+          <t>-5021.20521398334</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>540.57</t>
+          <t>-6268.4083573104</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>541.705</t>
+          <t>-4042.61140086197</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>521.77</t>
+          <t>-281655468.773129</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>575.275</t>
+          <t>-304641753.781213</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>511.188</t>
+          <t>-237589757.351026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>516.893</t>
+          <t>-270699284.22758</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>554.528</t>
+          <t>-339925933.615567</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>551.25</t>
+          <t>-360235934.177208</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>613.085</t>
+          <t>-421715974.951716</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>634.759</t>
+          <t>-418189264.651932</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>655.663</t>
+          <t>-459301255.081789</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>623.548</t>
+          <t>-455292137.152201</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>575.806</t>
+          <t>-436251147.604948</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>592.643</t>
+          <t>-466959655.987226</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>572.893</t>
+          <t>-472354557.598778</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>806.854</t>
+          <t>-687872349.39811</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>568.208</t>
+          <t>-440306324.415513</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3289.33855</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3301.17601</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3070.01195</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3277.96135</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3227.9768</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2970.60471</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3048.41562</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3366.44822</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>4252.8315</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4995.28712</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5266.43538</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5524.38471</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6331.55874</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>7278.69535</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6796.58128</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>263.441</t>
+          <t>0.0868375877693458</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>259.855</t>
+          <t>0.0844411225963697</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>258.156</t>
+          <t>0.0838519231944756</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>257.788</t>
+          <t>0.0931876921226079</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>258.328</t>
+          <t>0.0975833214213718</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>258.916</t>
+          <t>0.102128216922363</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>260.436</t>
+          <t>0.103786080531736</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>260.331</t>
+          <t>0.0959806155985757</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>269.335</t>
+          <t>0.0897022888199538</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>273.832</t>
+          <t>0.0906110527782375</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>275.243</t>
+          <t>0.0883078511689287</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>278.466</t>
+          <t>0.0894984570461261</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>283.387</t>
+          <t>0.0952905233591689</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>278.575</t>
+          <t>0.0931013251918401</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>282.012</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4009.30204461226</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4110.62893189141</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3985.18004554325</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4160.21885548685</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4226.76494684178</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3977.86902232336</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4095.1821265542</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4664.52482765077</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>6094.95444184257</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>7135.12399070072</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>7639.76272830467</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>8245.92046224411</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>9545.39955151358</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>11024.2451353322</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>10604.365021569</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>180.91</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>188.671</t>
+          <t>5428.85074392709</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>164.834</t>
+          <t>5270.72917188927</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>174.803</t>
+          <t>5483.52170324111</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>194.804</t>
+          <t>5598.45614178127</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>196.431</t>
+          <t>5290.57706587232</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>221.241</t>
+          <t>5477.72397844922</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>230.497</t>
+          <t>6144.2804408705</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>267.62</t>
+          <t>8016.30446858495</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>259.625</t>
+          <t>9440.96012703077</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>263.012</t>
+          <t>10170.0773856905</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>271.127</t>
+          <t>10905.9669471042</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>255.785</t>
+          <t>12486.3005746237</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>317.551</t>
+          <t>14467.4037383969</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>266.015</t>
+          <t>13817.1416338568</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>112.86</t>
+          <t>36529.8037857805</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>106.04</t>
+          <t>37487.7032509869</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>35563.213394576</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>36751.9667967827</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>110.62</t>
+          <t>36265.9523848064</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>32633.2348156165</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>96.11</t>
+          <t>33016.6545840697</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>92.21</t>
+          <t>36533.9452894855</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>45002.8512596556</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>53359.7893934907</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>57946.9071727335</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>82.38</t>
+          <t>62627.0932247143</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>101.89</t>
+          <t>72474.0691091171</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>86099.5392394877</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.716</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>5455.39135868644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>5645.12988085847</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.726</t>
+          <t>5745.15417948743</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>6005.84982413465</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.967</t>
+          <t>6349.97905401159</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>6647.25188224167</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>7098.23950453184</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>7575.489937585</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>8045.80011186733</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>8497.11821011226</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>8705.03496547207</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>8949.51823133714</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>9176.45124006597</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>9087.11431011384</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4009.30204461226</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4126.86311251552</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4270.32832980622</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4369.6860878491</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4512.5640103078</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4742.11401089715</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4921.84600579111</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5363.73180868011</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5738.08342482409</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6066.29332678926</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6391.84905601753</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6596.88058665277</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6858.45153611619</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7047.65434601301</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7008.56538602621</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3172.16004244469</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3165.50374607291</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2982.04383811073</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3424.83096675889</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3538.95208821873</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3332.77408412768</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3426.66917155078</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3506.5505591295</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4036.85876141505</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4834.98669296923</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5117.16685430948</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5605.02821289582</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>6906.09197537635</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>8015.98120160314</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>7436.5410161432</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>385081830.189556</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>388735218.183415</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>393173063.331875</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>400650693.290692</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>410295651.543646</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>421155000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>433872000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>443031000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>455955000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>458638000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>473113000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>494479000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>516413000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>540570000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>541705000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>556844000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>559558000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>565864000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>576508000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>590902000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>605960000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>626986000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>631030000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>652422000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>663882000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>679879000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>694745000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>715064000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>724744333.122296</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>725571484.03977</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>263441246.359666</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>259854833.536317</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>258155719.163838</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>257787648.463305</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>258328143.739714</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>258916000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>260436000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>260331000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>269335000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>273832000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>275243000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>278466000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>283387000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>278574974.798666</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>282012076.845781</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>297700</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>299500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>304100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>309800</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>314800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>321900</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>328300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>340800</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>353300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>366400</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>372400</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>384500</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>391166.670871672</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>392612.725033373</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>223716.495232719</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>225937.149256762</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>228763.11685584</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>233286.523036485</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>237983.052303308</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>241700</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>248200</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>255600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>262900</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>273900</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>285800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>308800</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>326600</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>325400</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>556844000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>559558000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>565864000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>576508000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>590902000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>605960000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>626986000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>631030000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>652422000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>663882000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>679879000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>694745000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>715064000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>724744333.122296</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>725571484.03977</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>385081830.189556</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>388735218.183415</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>393173063.331875</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>400650693.290692</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>410295651.543646</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>421155000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>433872000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>443031000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>455955000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>458638000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>473113000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>494479000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>516413000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>540570000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>541705000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.390116927880701</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.384904366830866</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.369970763777891</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.352881576519591</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.353397642917275</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.358280413431593</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.353910440875485</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.358248084348114</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.339631106733564</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.364859725162261</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.347331262498627</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.353356172580841</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.36971202850082</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.361581828929178</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.361957673459242</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.321293200762932</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.328626938735117</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.322348896331952</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.315242186789605</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.337233876652075</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.342979664793355</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.349594082475155</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.348925892107897</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.338509157324964</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.365575717545096</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.379463226115965</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.387763044649832</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.383128728066806</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.395468700852395</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.399773244605587</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.288589871356368</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.286468694434018</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.307680339890158</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.331876236690805</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.30936848043065</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.298739921775052</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.296495476649359</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.292826023543989</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.321859735941472</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.269564557292643</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.273205511385408</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.258880782769327</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.247159243432374</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.242949470218427</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.238269081935171</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.29501632942481</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.293308740062344</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.280608690472955</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.267314716451038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.267813512574648</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.271519071909591</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.271893085468395</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.278524698977206</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.280286225135778</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.279550377287939</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.265568736297898</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.274163910756846</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.293637463282541</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.302300726860568</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.302163821283627</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.359447173559755</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.367002576026058</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.358082664819624</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.347848501886329</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.371520788571168</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.377445256022587</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.382594963330836</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.380685901781172</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.390437025126417</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.403575019887614</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.416900756395004</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.428554835823112</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.420868018826323</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.425813446969654</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.429346185139048</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.345536497015435</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.339688683911597</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.361308644707421</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.384836781662633</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.360665698854184</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.351035672067821</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.345511951200769</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.340789399241622</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.329276749737806</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.316874602824447</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.317530507307097</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.297281253420042</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.285494517891135</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.271885826169778</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.268489993577326</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13745.56817</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14025.103</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>13541.08615</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>14456.44642</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>14904.16569</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>14176.64369</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14825.93409</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>16295.25573</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20252.26861</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>23628.63618</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>25577.21377</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>28109.62515</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>33700.83554</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>40127.54318</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>37463.21071</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>8457.07898</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8594.35449</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8252.77301</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8908.35267</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9137.40823</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8623.35115</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8904.39315</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9650.831</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>12053.16323</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>14275.94682</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>15287.24424</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>16510.99516</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>19392.39255</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>22483.38494</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>21253.68265</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>28225.7804786168</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28703.0313879198</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29087.669044844</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>29535.6804326495</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>29943.9567213731</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>30381.0747399953</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30840.3990575789</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>31403.4282774735</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31951.0194714376</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>32656.6168437408</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33395.9865417147</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>34307.1617116782</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>35470.9755419079</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>36716.5888590675</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
